--- a/exports/colleges/4417_shri-ram-college-of-commerce-srcc-new-delhi.xlsx
+++ b/exports/colleges/4417_shri-ram-college-of-commerce-srcc-new-delhi.xlsx
@@ -607,11 +607,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -619,7 +619,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="31" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -709,12 +709,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.25 Lakhs</t>
+          <t>1.25 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10+2 with 50%+CUET UG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CUET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Jan - 30 Jan 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.25 Lakhs</t>
+          <t>1.25 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10+2 with 50% + CUET UG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CUET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Jan - 30 Jan 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Post Graduate Diploma Global Business Operation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MBA/PGDM</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.28 Lakhs</t>
+          <t>3.28 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Graduation with 50%+SRCC GBO</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SRCC GBO</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 May - 09 Jun 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M.Com</t>
+          <t>Master of Commerce [M.Com]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Master of Commerce [M.Com]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -910,17 +910,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Graduation with 50%+CUET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CUET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 May - 04 Jul 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Graduation with 50%+CUET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CUET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 May - 04 Jul 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B.Com {Hons.}</t>
+          <t>Bachelor of Commerce [B.Com] {Hons.}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B.Com {Hons.}</t>
+          <t>Bachelor of Commerce [B.Com] {Hons.}</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 50%+CUET UG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CUET</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1066,27 +1066,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PG Diploma</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PG Diploma</t>
+          <t>Bachelor of Arts [BA] {Hons.} (Economics)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PG Diploma</t>
+          <t>Bachelor of Arts [BA] {Hons.} (Economics)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.28 Lakhs</t>
+          <t>1.25 Lakhs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 50% + CUET UG</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CUET</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1128,27 +1128,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BA {Hons.}</t>
+          <t>Post Graduate Diploma Global Business Operation</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BA {Hons.}</t>
+          <t>MBA/PGDM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.25 Lakhs</t>
+          <t>3.28 Lakhs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 50%+SRCC GBO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>SRCC GBO</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>M.Com</t>
+          <t>Master of Commerce [M.Com]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>M.Com</t>
+          <t>Master of Commerce [M.Com]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 50%+CUET PG</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CUET PG</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>Master of Arts [MA] (Economics)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>Master of Arts [MA] (Economics)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 50%+CUET PG</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CUET PG</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B.Com {Hons.} General</t>
+          <t>B.Com {Hons.}</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B.Com {Hons.} General</t>
+          <t>B.Com {Hons.}</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PG Diploma Global Business Operation</t>
+          <t>PG Diploma</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PG Diploma Global Business Operation</t>
+          <t>PG Diploma</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PG Diploma Global Business Operation</t>
+          <t>PG Diploma</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BA {Hons.} Economics</t>
+          <t>BA {Hons.}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BA {Hons.} Economics</t>
+          <t>BA {Hons.}</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M.Com (General)</t>
+          <t>M.Com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>M.Com</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1518,7 +1518,11 @@
           <t>83,190</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -1563,46 +1567,352 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>25,878</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B.Com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B.Com {Hons.} General</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>B.Com {Hons.} General</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.25 Lakhs</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PG Diploma Global Business Operation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PG Diploma Global Business Operation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PG Diploma Global Business Operation</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3.28 Lakhs</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BA {Hons.} Economics</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BA {Hons.} Economics</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.25 Lakhs</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>M.Com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>M.Com (General)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>83,190</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>MA (General)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>25,878</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>UG</t>
         </is>
